--- a/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Maya joue avec papa. Le soleil brille. Il fait chaud dans le jardin. Papa dit : le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Maya voit la lune. Elle voit les étoiles. Papa dit : la nuit, c'est la lune. Maya met son pyjama. Papa dit : la nuit, on fait dodo. Maya se couche. Elle ferme les yeux.</t>
+          <t>Le jour, Maya joue avec papa. Le soleil brille. Il fait chaud dans le jardin. Le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Maya voit la lune. Elle voit les étoiles. La nuit, c'est la lune. Maya met son pyjama. La nuit, on fait dodo. Maya se couche. Elle ferme les yeux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, Maya joue avec papa. Le soleil brille. Il fait chaud dans le jardin.
+papa|Le jour, c'est le soleil.
+narrateur|Le soir arrive. Le ciel devient bleu foncé. Maya voit la lune. Elle voit les étoiles.
+papa|La nuit, c'est la lune.
+narrateur|Maya met son pyjama.
+papa|La nuit, on fait dodo.
+narrateur|Maya se couche. Elle ferme les yeux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa baisse la lumière. Maya respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Maya se couche. Elle ferme les yeux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Maya a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Papa baisse la lumière. Maya respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le soleil de Maya</t>
+          <t>Le pique-nique de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut un pique-nique sous le cerisier. Le soleil chauffe les cerises. Une fourmi arrive sur la nappe. Le soir, la lune se pose dans les branches.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Maya joue avec papa. Le soleil brille. Il fait chaud dans le jardin. Le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Maya voit la lune. Elle voit les étoiles. La nuit, c'est la lune. Maya met son pyjama. La nuit, on fait dodo. Maya se couche. Elle ferme les yeux.</t>
+          <t>Les cerises encore vertes pendent au dessus du bac. L'herbe est encore mouillée, fraîche. Un merle picore sous le cerisier. Le tronc est chaud d'un côté. Tu as vu le merle, Nino ? Il saute. Oui. Il cherche un ver. Je veux un pique nique. Sous le cerisier ? Oui. En ce moment, Nino tire la nappe. La nappe sent le tiroir. Il la pose dans l'herbe. Le soleil chauffe les cerises, au dessus. Des ronds d'ombre bougent sur le tissu. Le jour est chaud. Le soleil est sur l'arbre. Papa pose le pain. Nino pose deux pommes. Et le fromage. Une fourmi arrive sur la nappe. Elle est toute petite, noire. Oh. Une fourmi. Elle veut la mie ? C'est notre pain. Nino souffle tout doux. La fourmi ne part pas. On avance le pain un peu ? Oui. Nino pousse le pain. La fourmi reste sur le coin. Ils mangent de l'autre côté. Merci, Nino. Tu as laissé la fourmi. Le pain a des miettes. Une cerise tombe près du bac. Elle est dure. Pas encore mûre. L'ombre du cerisier s'allonge. L'air refroidit les bras. Le jour s'en va. Le merle est parti. Le ciel devient bleu foncé. Une lune ronde se pose dans les branches. Elle est dans l'arbre. La nuit est là. La lune est sur le cerisier. On range la nappe ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le jour, Maya joue avec papa. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Il fait chaud dans le jardin. Papa dit : le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Maya voit la lune. Elle voit les étoiles. Papa dit : la nuit, c'est la lune. Maya met son pyjama. Papa dit : la nuit, on fait dodo. Maya se couche. Elle ferme les yeux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les cerises encore vertes pendent au dessus du bac. L'herbe est encore mouillée, fraîche. Un merle picore sous le cerisier. Le tronc est chaud d'un côté. Tu as vu le merle, Nino ? Il saute. Oui. Il cherche un ver. Je veux un pique nique. Sous le cerisier ? Oui. En ce moment, Nino tire la nappe. La nappe sent le tiroir. Il la pose dans l'herbe. Le soleil chauffe les cerises, au dessus. Des ronds d'ombre bougent sur le tissu. Le jour est chaud. Le soleil est sur l'arbre. Papa pose le pain. Nino pose deux pommes. Et le fromage. Une fourmi arrive sur la nappe. Elle est toute petite, noire. Oh. Une fourmi. Elle veut la mie ? C'est notre pain. Nino souffle tout doux. La fourmi ne part pas. On avance le pain un peu ? Oui. Nino pousse le pain. La fourmi reste sur le coin. Ils mangent de l'autre côté. Merci, Nino. Tu as laissé la fourmi. Le pain a des miettes. Une cerise tombe près du bac. Elle est dure. Pas encore mûre. L'ombre du cerisier s'allonge. L'air refroidit les bras. Le jour s'en va. Le merle est parti. Le ciel devient bleu foncé. Une lune ronde se pose dans les branches. Elle est dans l'arbre. La nuit est là. La lune est sur le cerisier. On range la nappe ? Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le jour, Maya joue avec papa. Le soleil brille. Il fait chaud dans le jardin.
-papa|Le jour, c'est le soleil.
-narrateur|Le soir arrive. Le ciel devient bleu foncé. Maya voit la lune. Elle voit les étoiles.
-papa|La nuit, c'est la lune.
-narrateur|Maya met son pyjama.
-papa|La nuit, on fait dodo.
-narrateur|Maya se couche. Elle ferme les yeux.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les cerises encore vertes pendent au dessus du bac.
+narrateur|L'herbe est encore mouillée, fraîche.
+narrateur|Un merle picore sous le cerisier.
+narrateur|Le tronc est chaud d'un côté.
+papa|Tu as vu le merle, Nino ?
+enfant-m|Il saute.
+papa|Oui.
+papa|Il cherche un ver.
+enfant-m|Je veux un pique nique.
+papa|Sous le cerisier ?
+enfant-m|Oui.
+narrateur|En ce moment, Nino tire la nappe.
+narrateur|La nappe sent le tiroir.
+narrateur|Il la pose dans l'herbe.
+narrateur|Le soleil chauffe les cerises, au dessus.
+narrateur|Des ronds d'ombre bougent sur le tissu.
+papa|Le jour est chaud.
+papa|Le soleil est sur l'arbre.
+narrateur|Papa pose le pain.
+narrateur|Nino pose deux pommes.
+enfant-m|Et le fromage.
+narrateur|Une fourmi arrive sur la nappe.
+narrateur|Elle est toute petite, noire.
+enfant-m|Oh.
+enfant-m|Une fourmi.
+papa|Elle veut la mie ?
+enfant-m|C'est notre pain.
+narrateur|Nino souffle tout doux.
+narrateur|La fourmi ne part pas.
+papa|On avance le pain un peu ?
+enfant-m|Oui.
+narrateur|Nino pousse le pain.
+narrateur|La fourmi reste sur le coin.
+narrateur|Ils mangent de l'autre côté.
+papa|Merci, Nino.
+papa|Tu as laissé la fourmi.
+narrateur|Le pain a des miettes.
+narrateur|Une cerise tombe près du bac.
+enfant-m|Elle est dure.
+papa|Pas encore mûre.
+narrateur|L'ombre du cerisier s'allonge.
+narrateur|L'air refroidit les bras.
+papa|Le jour s'en va.
+enfant-m|Le merle est parti.
+narrateur|Le ciel devient bleu foncé.
+narrateur|Une lune ronde se pose dans les branches.
+enfant-m|Elle est dans l'arbre.
+papa|La nuit est là.
+papa|La lune est sur le cerisier.
+papa|On range la nappe ?
+enfant-m|Oui.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseaux,jardin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La lune est là. Quel moment est-ce ?</t>
+          <t>La lune est dans les branches. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là. Quel moment est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lune est dans les branches. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1366,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nuit | la nuit | lune | le soir</t>
+          <t>nuit | la nuit | le soir | dodo | c'est la nuit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>La lune vient la nuit. Quel moment ?</t>
+          <t>La lune est dans l'arbre. C'est le jour, ou la nuit ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1490,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La lune est dans les branches.
+narrateur|Quel moment est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
+          <t>Nino a mangé sous le cerisier. Le soleil était sur les cerises. Maintenant la lune est dans l'arbre. Le jour, c'était le soleil. La nuit, c'est la lune. Elle est ronde. Oui. On rentre se coucher ? Encore un peu. La fourmi a quitté le coin. La nappe a une tache de mie. Tu plies ton côté ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a mangé sous le cerisier. Le soleil était sur les cerises. Maintenant la lune est dans l'arbre. Le jour, c'était le soleil. La nuit, c'est la lune. Elle est ronde. Oui. On rentre se coucher ? Encore un peu. La fourmi a quitté le coin. La nappe a une tache de mie. Tu plies ton côté ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,14 +1655,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1738,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a mangé sous le cerisier.
+narrateur|Le soleil était sur les cerises.
+narrateur|Maintenant la lune est dans l'arbre.
+papa|Le jour, c'était le soleil.
+papa|La nuit, c'est la lune.
+enfant-m|Elle est ronde.
+papa|Oui.
+papa|On rentre se coucher ?
+enfant-m|Encore un peu.
+narrateur|La fourmi a quitté le coin.
+narrateur|La nappe a une tache de mie.
+papa|Tu plies ton côté ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa baisse la lumière. Maya respire.</t>
+          <t>Nino plie la nappe, tout croche. Papa prend le pain. Ils rentrent, l'herbe froide aux chevilles. Le pyjama, maintenant. Le pyjama est doux, un peu rêche aux poignets. La lune est encore là ? À la fenêtre. Nino monte sur le lit. Le cerisier est noir, dehors. La lune tient encore une branche. La nuit, on fait dodo. Tu fermes les yeux ? Presque. Papa baisse la lumière. Nino respire le savon du drap.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lumière. Maya respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino plie la nappe, tout croche. Papa prend le pain. Ils rentrent, l'herbe froide aux chevilles. Le pyjama, maintenant. Le pyjama est doux, un peu rêche aux poignets. La lune est encore là ? À la fenêtre. Nino monte sur le lit. Le cerisier est noir, dehors. La lune tient encore une branche. La nuit, on fait dodo. Tu fermes les yeux ? Presque. Papa baisse la lumière. Nino respire le savon du drap.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1838,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1917,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa baisse la lumière. Maya respire.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino plie la nappe, tout croche.
+narrateur|Papa prend le pain.
+narrateur|Ils rentrent, l'herbe froide aux chevilles.
+papa|Le pyjama, maintenant.
+narrateur|Le pyjama est doux, un peu rêche aux poignets.
+enfant-m|La lune est encore là ?
+papa|À la fenêtre.
+narrateur|Nino monte sur le lit.
+narrateur|Le cerisier est noir, dehors.
+narrateur|La lune tient encore une branche.
+papa|La nuit, on fait dodo.
+papa|Tu fermes les yeux ?
+enfant-m|Presque.
+narrateur|Papa baisse la lumière.
+narrateur|Nino respire le savon du drap.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une cerise bouge encore, dehors. La lune la touche, toute pâle. Notre nappe est pliée. Oui. Le pique nique est fini. Nino ferme les yeux. Le merle se tait, déjà.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une cerise bouge encore, dehors. La lune la touche, toute pâle. Notre nappe est pliée. Oui. Le pique nique est fini. Nino ferme les yeux. Le merle se tait, déjà.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1935,14 +2019,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2014,10 +2098,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Une cerise bouge encore, dehors.
+narrateur|La lune la touche, toute pâle.
+enfant-m|Notre nappe est pliée.
+papa|Oui.
+papa|Le pique nique est fini.
+narrateur|Nino ferme les yeux.
+narrateur|Le merle se tait, déjà.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison et jardin</t>
+          <t>jardin, cerisier, nappe</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
